--- a/小野町_引継ぎ_整理済/07_介護保険_見える化整理/小野町_第10期介護保険事業計画_供給体制・介護予防整理.xlsx
+++ b/小野町_引継ぎ_整理済/07_介護保険_見える化整理/小野町_第10期介護保険事業計画_供給体制・介護予防整理.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_入所定員" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_通いの場" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_総合事業サービス" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90_取込確認" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_認知症施策" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90_取込確認" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3306,7 +3307,193 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>指標ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>指標名</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>前回</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>直近</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>J16</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>初期集中支援チームの実施状況（訪問実績）</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>訪問実績（延べ件数）</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>R2→R5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>J17</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>認知症地域支援推進員配置状況（配置人数）</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>配置人数</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>R2→R5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>J18</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>認知症カフェ設置状況（設置主体別箇所数）</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>設置主体別箇所数</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>令和3年4月→令和6年4月</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>公表されているのはJ16・J17・J18の3指標のみ。研修系（J1〜J15）は本町の値が未公表</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>初期集中支援チームの訪問実績は令和2年度・令和5年度とも0件（県内59団体中30団体が0件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>認知症地域支援推進員は1人（令和3年3月）から4人（令和6年3月）へ増員。県内中央値3人</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>認知症カフェは1か所で横ばい。県内中央値1か所</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4396,6 +4583,87 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>認知症施策</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>J16</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>J16_初期集中支援チームの実施状況（訪問実績）_時系列.xlsx</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>小野町</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2件</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>認知症施策</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>J17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>J17_認知症地域支援推進員配置状況（配置人数）_時系列.xlsx</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>小野町</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2件</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>認知症施策</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>J18</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>J18_認知症カフェ設置状況（設置主体別箇所数）_時系列.xlsx</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>小野町</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2件</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
